--- a/artfynd/A 25757-2023 artfynd.xlsx
+++ b/artfynd/A 25757-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123663914</v>
       </c>
       <c r="B2" t="n">
-        <v>91589</v>
+        <v>91606</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 25757-2023 artfynd.xlsx
+++ b/artfynd/A 25757-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123663914</v>
       </c>
       <c r="B2" t="n">
-        <v>91606</v>
+        <v>91611</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 25757-2023 artfynd.xlsx
+++ b/artfynd/A 25757-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123663914</v>
       </c>
       <c r="B2" t="n">
-        <v>91611</v>
+        <v>91613</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
